--- a/artfynd/A 32767-2026 artfynd.xlsx
+++ b/artfynd/A 32767-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135791296</v>
       </c>
       <c r="B2" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32767-2026 artfynd.xlsx
+++ b/artfynd/A 32767-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135791296</v>
       </c>
       <c r="B2" t="n">
-        <v>98138</v>
+        <v>98155</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32767-2026 artfynd.xlsx
+++ b/artfynd/A 32767-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135791296</v>
       </c>
       <c r="B2" t="n">
-        <v>98155</v>
+        <v>98156</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32767-2026 artfynd.xlsx
+++ b/artfynd/A 32767-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135791296</v>
       </c>
       <c r="B2" t="n">
-        <v>98156</v>
+        <v>98157</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32767-2026 artfynd.xlsx
+++ b/artfynd/A 32767-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135791296</v>
       </c>
       <c r="B2" t="n">
-        <v>98157</v>
+        <v>98158</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32767-2026 artfynd.xlsx
+++ b/artfynd/A 32767-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135791296</v>
       </c>
       <c r="B2" t="n">
-        <v>98158</v>
+        <v>98164</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32767-2026 artfynd.xlsx
+++ b/artfynd/A 32767-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135791296</v>
       </c>
       <c r="B2" t="n">
-        <v>98164</v>
+        <v>98165</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32767-2026 artfynd.xlsx
+++ b/artfynd/A 32767-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135791296</v>
       </c>
       <c r="B2" t="n">
-        <v>98165</v>
+        <v>98176</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32767-2026 artfynd.xlsx
+++ b/artfynd/A 32767-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135791296</v>
       </c>
       <c r="B2" t="n">
-        <v>98176</v>
+        <v>98189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32767-2026 artfynd.xlsx
+++ b/artfynd/A 32767-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135791296</v>
       </c>
       <c r="B2" t="n">
-        <v>98189</v>
+        <v>98190</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
